--- a/NFL Barbook Trivia.xlsx
+++ b/NFL Barbook Trivia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fortmans/code/barbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E646A1F5-2D44-9048-AF4E-DBAAF92E6F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9065A36-AFBC-F046-8F56-BB7FDEE39CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="520">
   <si>
     <t>📚  Page Configuration Editor</t>
   </si>
@@ -1389,12 +1389,246 @@
   <si>
     <t>Easy</t>
   </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Aaron Rodgers</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Aaron Rodgers</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/R/RodgAa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Tom Brady</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Tom Brady</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/B/BradTo00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Drew Brees</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Drew Brees</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/B/BreeDr00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Peyton Manning</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Peyton Manning</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MannPe00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Brett Favre</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Brett Favre</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/F/FavrBr00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Philip Rivers</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Philip Rivers</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/R/RivePh00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Matthew Stafford</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Matthew Stafford</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/S/StafMa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Dan Marino</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Dan Marino</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MariDa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Ben Roethlisberger</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Ben Roethlisberger</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/R/RoetBe00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Matt Ryan</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Matt Ryan</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/R/RyanMa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Eli Manning</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Eli Manning</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MannEl00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Russell Wilson</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Russell Wilson</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/W/WilsRu00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Fran Tarkenton</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Fran Tarkenton</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/T/TarkFr00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by John Elway</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from John Elway</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/E/ElwaJo00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Kirk Cousins</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Kirk Cousins</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/C/CousKi00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Carson Palmer</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Carson Palmer</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/P/PalmCa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Warren Moon</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Warren Moon</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MoonWa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Johnny Unitas</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Johnny Unitas</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/U/UnitJo00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Vinny Testaverde</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Vinny Testaverde</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/T/TestVi00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Joe Montana</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Joe Montana</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MontJo01/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Joe Flacco</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Joe Flacco</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/F/FlacJo00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Patrick Mahomes</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Patrick Mahomes</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/M/MahoPa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Dave Krieg</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Dave Krieg</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/K/KrieDa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Derek Carr</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Derek Carr</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/C/CarrDe02/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Jared Goff</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Jared Goff</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/G/GoffJa00/touchdowns/passing</t>
+  </si>
+  <si>
+    <t>Top 10 player with the most receiving touchdowns thrown by Sonny Jurgensen</t>
+  </si>
+  <si>
+    <t>List the top 10 wide receivers with the most receiving touchdowns from Sonny Jurgensen</t>
+  </si>
+  <si>
+    <t>https://www.pro-football-reference.com/players/J/JurgSo00/touchdowns/passing</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1534,6 +1768,19 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1686,7 +1933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1784,11 +2031,81 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2055,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M996"/>
+  <dimension ref="A1:Z996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -2073,7 +2390,7 @@
     <col min="14" max="28" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -2090,7 +2407,7 @@
       <c r="L1" s="26"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -2107,8 +2424,8 @@
       <c r="L2" s="26"/>
       <c r="M2" s="27"/>
     </row>
-    <row r="3" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2149,7 +2466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -2190,7 +2507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -2223,7 +2540,7 @@
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
     </row>
-    <row r="7" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2256,7 +2573,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -2289,7 +2606,7 @@
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
     </row>
-    <row r="9" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -2322,7 +2639,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -2355,7 +2672,7 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -2388,7 +2705,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -2429,7 +2746,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -2470,7 +2787,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -2511,7 +2828,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -2552,7 +2869,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -2593,7 +2910,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -2626,7 +2943,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -2766,7 +3083,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -2799,7 +3116,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -2832,7 +3149,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -2865,7 +3182,7 @@
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -2898,7 +3215,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -2931,7 +3248,7 @@
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -2964,7 +3281,7 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -2997,7 +3314,7 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -3030,7 +3347,7 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -3063,7 +3380,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -3096,7 +3413,7 @@
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -3129,7 +3446,7 @@
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -3162,7 +3479,7 @@
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -3195,7 +3512,7 @@
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
     </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -3228,7 +3545,7 @@
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
     </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -3261,7 +3578,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
     </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -3294,7 +3611,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
     </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -3327,7 +3644,7 @@
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
     </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -3360,7 +3677,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
     </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>36</v>
       </c>
@@ -3393,7 +3710,7 @@
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
     </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>37</v>
       </c>
@@ -3426,7 +3743,7 @@
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>38</v>
       </c>
@@ -3459,7 +3776,7 @@
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>39</v>
       </c>
@@ -3492,7 +3809,7 @@
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -3525,7 +3842,7 @@
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>41</v>
       </c>
@@ -3558,7 +3875,7 @@
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>42</v>
       </c>
@@ -3591,7 +3908,7 @@
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>43</v>
       </c>
@@ -3624,7 +3941,7 @@
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>44</v>
       </c>
@@ -3657,7 +3974,7 @@
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
     </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>45</v>
       </c>
@@ -3690,7 +4007,7 @@
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
     </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>46</v>
       </c>
@@ -3723,7 +4040,7 @@
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
     </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>47</v>
       </c>
@@ -3756,7 +4073,7 @@
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
     </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -3789,7 +4106,7 @@
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
     </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -3822,7 +4139,7 @@
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
     </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -3855,7 +4172,7 @@
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
     </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -3888,7 +4205,7 @@
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
     </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>52</v>
       </c>
@@ -3921,7 +4238,7 @@
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
     </row>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>53</v>
       </c>
@@ -3954,7 +4271,7 @@
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
     </row>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>54</v>
       </c>
@@ -3987,7 +4304,7 @@
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
     </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>55</v>
       </c>
@@ -4020,7 +4337,7 @@
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
     </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>56</v>
       </c>
@@ -4053,7 +4370,7 @@
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
     </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>57</v>
       </c>
@@ -4086,7 +4403,7 @@
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
     </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>58</v>
       </c>
@@ -4119,7 +4436,7 @@
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
     </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>59</v>
       </c>
@@ -4152,7 +4469,7 @@
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
     </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>60</v>
       </c>
@@ -4185,7 +4502,7 @@
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
     </row>
-    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>61</v>
       </c>
@@ -4218,7 +4535,7 @@
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
     </row>
-    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>62</v>
       </c>
@@ -4251,7 +4568,7 @@
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
     </row>
-    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>63</v>
       </c>
@@ -4284,7 +4601,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
     </row>
-    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>64</v>
       </c>
@@ -4317,7 +4634,7 @@
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
     </row>
-    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>65</v>
       </c>
@@ -4350,7 +4667,7 @@
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
     </row>
-    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>66</v>
       </c>
@@ -4383,7 +4700,7 @@
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
     </row>
-    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>67</v>
       </c>
@@ -4416,7 +4733,7 @@
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
     </row>
-    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>68</v>
       </c>
@@ -4449,7 +4766,7 @@
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
     </row>
-    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>69</v>
       </c>
@@ -4482,7 +4799,7 @@
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
     </row>
-    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>70</v>
       </c>
@@ -4515,7 +4832,7 @@
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
     </row>
-    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>71</v>
       </c>
@@ -4548,7 +4865,7 @@
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
     </row>
-    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>72</v>
       </c>
@@ -4581,7 +4898,7 @@
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
     </row>
-    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>73</v>
       </c>
@@ -4614,7 +4931,7 @@
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
     </row>
-    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>74</v>
       </c>
@@ -4647,7 +4964,7 @@
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
     </row>
-    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>75</v>
       </c>
@@ -4680,7 +4997,7 @@
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
     </row>
-    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>76</v>
       </c>
@@ -4713,7 +5030,7 @@
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>77</v>
       </c>
@@ -4746,7 +5063,7 @@
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
     </row>
-    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>78</v>
       </c>
@@ -4779,7 +5096,7 @@
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
     </row>
-    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>79</v>
       </c>
@@ -4812,7 +5129,7 @@
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>80</v>
       </c>
@@ -4845,7 +5162,7 @@
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
     </row>
-    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>81</v>
       </c>
@@ -4878,7 +5195,7 @@
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
     </row>
-    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>82</v>
       </c>
@@ -4911,7 +5228,7 @@
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
     </row>
-    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>83</v>
       </c>
@@ -4944,7 +5261,7 @@
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
     </row>
-    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>84</v>
       </c>
@@ -4977,7 +5294,7 @@
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
     </row>
-    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>85</v>
       </c>
@@ -5010,7 +5327,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
     </row>
-    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>86</v>
       </c>
@@ -5043,7 +5360,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
     </row>
-    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>87</v>
       </c>
@@ -5076,7 +5393,7 @@
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
     </row>
-    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>88</v>
       </c>
@@ -5107,7 +5424,7 @@
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
     </row>
-    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>89</v>
       </c>
@@ -5138,7 +5455,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
     </row>
-    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>90</v>
       </c>
@@ -5169,7 +5486,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
     </row>
-    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>91</v>
       </c>
@@ -5202,7 +5519,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
     </row>
-    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>92</v>
       </c>
@@ -5233,7 +5550,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>93</v>
       </c>
@@ -5264,7 +5581,7 @@
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
     </row>
-    <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>94</v>
       </c>
@@ -5295,7 +5612,7 @@
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
     </row>
-    <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>95</v>
       </c>
@@ -5326,7 +5643,7 @@
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
     </row>
-    <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>96</v>
       </c>
@@ -5359,7 +5676,7 @@
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
     </row>
-    <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>97</v>
       </c>
@@ -5390,7 +5707,7 @@
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
     </row>
-    <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>98</v>
       </c>
@@ -5421,7 +5738,7 @@
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>99</v>
       </c>
@@ -5454,7 +5771,7 @@
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
     </row>
-    <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>100</v>
       </c>
@@ -5487,7 +5804,7 @@
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
     </row>
-    <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>101</v>
       </c>
@@ -5520,7 +5837,7 @@
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
     </row>
-    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>102</v>
       </c>
@@ -5553,7 +5870,7 @@
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
     </row>
-    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>103</v>
       </c>
@@ -5586,7 +5903,7 @@
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
     </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>104</v>
       </c>
@@ -5619,7 +5936,7 @@
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
     </row>
-    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>105</v>
       </c>
@@ -5652,7 +5969,7 @@
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
     </row>
-    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>106</v>
       </c>
@@ -5685,7 +6002,7 @@
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
     </row>
-    <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>107</v>
       </c>
@@ -5718,7 +6035,7 @@
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
     </row>
-    <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ht="28" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>108</v>
       </c>
@@ -5751,7 +6068,7 @@
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
     </row>
-    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" ht="28" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>109</v>
       </c>
@@ -5784,7 +6101,7 @@
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" ht="28" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>110</v>
       </c>
@@ -5817,7 +6134,7 @@
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" ht="28" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>111</v>
       </c>
@@ -5850,7 +6167,7 @@
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" ht="28" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>112</v>
       </c>
@@ -5883,34 +6200,1204 @@
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A117" s="2">
+        <v>113</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G117" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H117" s="4">
+        <v>1</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="J117" s="4"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="35"/>
+      <c r="O117" s="35"/>
+      <c r="P117" s="35"/>
+      <c r="Q117" s="35"/>
+      <c r="R117" s="35"/>
+      <c r="S117" s="35"/>
+      <c r="T117" s="35"/>
+      <c r="U117" s="35"/>
+      <c r="V117" s="35"/>
+      <c r="W117" s="35"/>
+      <c r="X117" s="35"/>
+      <c r="Y117" s="35"/>
+      <c r="Z117" s="35"/>
+    </row>
+    <row r="118" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A118" s="2">
+        <v>114</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G118" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H118" s="4">
+        <v>1</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J118" s="4"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="35"/>
+      <c r="O118" s="35"/>
+      <c r="P118" s="35"/>
+      <c r="Q118" s="35"/>
+      <c r="R118" s="35"/>
+      <c r="S118" s="35"/>
+      <c r="T118" s="35"/>
+      <c r="U118" s="35"/>
+      <c r="V118" s="35"/>
+      <c r="W118" s="35"/>
+      <c r="X118" s="35"/>
+      <c r="Y118" s="35"/>
+      <c r="Z118" s="35"/>
+    </row>
+    <row r="119" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A119" s="2">
+        <v>115</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G119" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H119" s="4">
+        <v>1</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="J119" s="4"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="35"/>
+      <c r="O119" s="35"/>
+      <c r="P119" s="35"/>
+      <c r="Q119" s="35"/>
+      <c r="R119" s="35"/>
+      <c r="S119" s="35"/>
+      <c r="T119" s="35"/>
+      <c r="U119" s="35"/>
+      <c r="V119" s="35"/>
+      <c r="W119" s="35"/>
+      <c r="X119" s="35"/>
+      <c r="Y119" s="35"/>
+      <c r="Z119" s="35"/>
+    </row>
+    <row r="120" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A120" s="2">
+        <v>116</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G120" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H120" s="4">
+        <v>1</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="J120" s="4"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="35"/>
+      <c r="O120" s="35"/>
+      <c r="P120" s="35"/>
+      <c r="Q120" s="35"/>
+      <c r="R120" s="35"/>
+      <c r="S120" s="35"/>
+      <c r="T120" s="35"/>
+      <c r="U120" s="35"/>
+      <c r="V120" s="35"/>
+      <c r="W120" s="35"/>
+      <c r="X120" s="35"/>
+      <c r="Y120" s="35"/>
+      <c r="Z120" s="35"/>
+    </row>
+    <row r="121" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A121" s="2">
+        <v>117</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H121" s="4">
+        <v>1</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="J121" s="4"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="35"/>
+      <c r="O121" s="35"/>
+      <c r="P121" s="35"/>
+      <c r="Q121" s="35"/>
+      <c r="R121" s="35"/>
+      <c r="S121" s="35"/>
+      <c r="T121" s="35"/>
+      <c r="U121" s="35"/>
+      <c r="V121" s="35"/>
+      <c r="W121" s="35"/>
+      <c r="X121" s="35"/>
+      <c r="Y121" s="35"/>
+      <c r="Z121" s="35"/>
+    </row>
+    <row r="122" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A122" s="2">
+        <v>118</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G122" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H122" s="4">
+        <v>1</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="J122" s="4"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="35"/>
+      <c r="O122" s="35"/>
+      <c r="P122" s="35"/>
+      <c r="Q122" s="35"/>
+      <c r="R122" s="35"/>
+      <c r="S122" s="35"/>
+      <c r="T122" s="35"/>
+      <c r="U122" s="35"/>
+      <c r="V122" s="35"/>
+      <c r="W122" s="35"/>
+      <c r="X122" s="35"/>
+      <c r="Y122" s="35"/>
+      <c r="Z122" s="35"/>
+    </row>
+    <row r="123" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A123" s="2">
+        <v>119</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G123" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H123" s="4">
+        <v>1</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J123" s="4"/>
+      <c r="K123" s="6"/>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="35"/>
+      <c r="O123" s="35"/>
+      <c r="P123" s="35"/>
+      <c r="Q123" s="35"/>
+      <c r="R123" s="35"/>
+      <c r="S123" s="35"/>
+      <c r="T123" s="35"/>
+      <c r="U123" s="35"/>
+      <c r="V123" s="35"/>
+      <c r="W123" s="35"/>
+      <c r="X123" s="35"/>
+      <c r="Y123" s="35"/>
+      <c r="Z123" s="35"/>
+    </row>
+    <row r="124" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A124" s="2">
+        <v>120</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G124" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H124" s="4">
+        <v>1</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J124" s="4"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="35"/>
+      <c r="O124" s="35"/>
+      <c r="P124" s="35"/>
+      <c r="Q124" s="35"/>
+      <c r="R124" s="35"/>
+      <c r="S124" s="35"/>
+      <c r="T124" s="35"/>
+      <c r="U124" s="35"/>
+      <c r="V124" s="35"/>
+      <c r="W124" s="35"/>
+      <c r="X124" s="35"/>
+      <c r="Y124" s="35"/>
+      <c r="Z124" s="35"/>
+    </row>
+    <row r="125" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A125" s="2">
+        <v>121</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G125" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H125" s="4">
+        <v>1</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="J125" s="4"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="35"/>
+      <c r="O125" s="35"/>
+      <c r="P125" s="35"/>
+      <c r="Q125" s="35"/>
+      <c r="R125" s="35"/>
+      <c r="S125" s="35"/>
+      <c r="T125" s="35"/>
+      <c r="U125" s="35"/>
+      <c r="V125" s="35"/>
+      <c r="W125" s="35"/>
+      <c r="X125" s="35"/>
+      <c r="Y125" s="35"/>
+      <c r="Z125" s="35"/>
+    </row>
+    <row r="126" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A126" s="2">
+        <v>122</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G126" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H126" s="4">
+        <v>1</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="J126" s="4"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+      <c r="N126" s="35"/>
+      <c r="O126" s="35"/>
+      <c r="P126" s="35"/>
+      <c r="Q126" s="35"/>
+      <c r="R126" s="35"/>
+      <c r="S126" s="35"/>
+      <c r="T126" s="35"/>
+      <c r="U126" s="35"/>
+      <c r="V126" s="35"/>
+      <c r="W126" s="35"/>
+      <c r="X126" s="35"/>
+      <c r="Y126" s="35"/>
+      <c r="Z126" s="35"/>
+    </row>
+    <row r="127" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A127" s="2">
+        <v>123</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G127" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H127" s="4">
+        <v>1</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="J127" s="4"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="35"/>
+      <c r="O127" s="35"/>
+      <c r="P127" s="35"/>
+      <c r="Q127" s="35"/>
+      <c r="R127" s="35"/>
+      <c r="S127" s="35"/>
+      <c r="T127" s="35"/>
+      <c r="U127" s="35"/>
+      <c r="V127" s="35"/>
+      <c r="W127" s="35"/>
+      <c r="X127" s="35"/>
+      <c r="Y127" s="35"/>
+      <c r="Z127" s="35"/>
+    </row>
+    <row r="128" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A128" s="2">
+        <v>124</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G128" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H128" s="4">
+        <v>1</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="J128" s="4"/>
+      <c r="K128" s="6"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="35"/>
+      <c r="O128" s="35"/>
+      <c r="P128" s="35"/>
+      <c r="Q128" s="35"/>
+      <c r="R128" s="35"/>
+      <c r="S128" s="35"/>
+      <c r="T128" s="35"/>
+      <c r="U128" s="35"/>
+      <c r="V128" s="35"/>
+      <c r="W128" s="35"/>
+      <c r="X128" s="35"/>
+      <c r="Y128" s="35"/>
+      <c r="Z128" s="35"/>
+    </row>
+    <row r="129" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A129" s="2">
+        <v>125</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G129" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H129" s="4">
+        <v>1</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="J129" s="4"/>
+      <c r="K129" s="6"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="35"/>
+      <c r="O129" s="35"/>
+      <c r="P129" s="35"/>
+      <c r="Q129" s="35"/>
+      <c r="R129" s="35"/>
+      <c r="S129" s="35"/>
+      <c r="T129" s="35"/>
+      <c r="U129" s="35"/>
+      <c r="V129" s="35"/>
+      <c r="W129" s="35"/>
+      <c r="X129" s="35"/>
+      <c r="Y129" s="35"/>
+      <c r="Z129" s="35"/>
+    </row>
+    <row r="130" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A130" s="2">
+        <v>126</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G130" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H130" s="4">
+        <v>1</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="J130" s="4"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="35"/>
+      <c r="O130" s="35"/>
+      <c r="P130" s="35"/>
+      <c r="Q130" s="35"/>
+      <c r="R130" s="35"/>
+      <c r="S130" s="35"/>
+      <c r="T130" s="35"/>
+      <c r="U130" s="35"/>
+      <c r="V130" s="35"/>
+      <c r="W130" s="35"/>
+      <c r="X130" s="35"/>
+      <c r="Y130" s="35"/>
+      <c r="Z130" s="35"/>
+    </row>
+    <row r="131" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A131" s="2">
+        <v>127</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G131" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H131" s="4">
+        <v>1</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="J131" s="4"/>
+      <c r="K131" s="6"/>
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="35"/>
+      <c r="O131" s="35"/>
+      <c r="P131" s="35"/>
+      <c r="Q131" s="35"/>
+      <c r="R131" s="35"/>
+      <c r="S131" s="35"/>
+      <c r="T131" s="35"/>
+      <c r="U131" s="35"/>
+      <c r="V131" s="35"/>
+      <c r="W131" s="35"/>
+      <c r="X131" s="35"/>
+      <c r="Y131" s="35"/>
+      <c r="Z131" s="35"/>
+    </row>
+    <row r="132" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A132" s="2">
+        <v>128</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G132" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H132" s="4">
+        <v>1</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="J132" s="4"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="35"/>
+      <c r="O132" s="35"/>
+      <c r="P132" s="35"/>
+      <c r="Q132" s="35"/>
+      <c r="R132" s="35"/>
+      <c r="S132" s="35"/>
+      <c r="T132" s="35"/>
+      <c r="U132" s="35"/>
+      <c r="V132" s="35"/>
+      <c r="W132" s="35"/>
+      <c r="X132" s="35"/>
+      <c r="Y132" s="35"/>
+      <c r="Z132" s="35"/>
+    </row>
+    <row r="133" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A133" s="2">
+        <v>129</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G133" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H133" s="4">
+        <v>1</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="J133" s="4"/>
+      <c r="K133" s="6"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="35"/>
+      <c r="O133" s="35"/>
+      <c r="P133" s="35"/>
+      <c r="Q133" s="35"/>
+      <c r="R133" s="35"/>
+      <c r="S133" s="35"/>
+      <c r="T133" s="35"/>
+      <c r="U133" s="35"/>
+      <c r="V133" s="35"/>
+      <c r="W133" s="35"/>
+      <c r="X133" s="35"/>
+      <c r="Y133" s="35"/>
+      <c r="Z133" s="35"/>
+    </row>
+    <row r="134" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A134" s="2">
+        <v>130</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G134" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H134" s="4">
+        <v>1</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="J134" s="4"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="35"/>
+      <c r="O134" s="35"/>
+      <c r="P134" s="35"/>
+      <c r="Q134" s="35"/>
+      <c r="R134" s="35"/>
+      <c r="S134" s="35"/>
+      <c r="T134" s="35"/>
+      <c r="U134" s="35"/>
+      <c r="V134" s="35"/>
+      <c r="W134" s="35"/>
+      <c r="X134" s="35"/>
+      <c r="Y134" s="35"/>
+      <c r="Z134" s="35"/>
+    </row>
+    <row r="135" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A135" s="2">
+        <v>131</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G135" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H135" s="4">
+        <v>1</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J135" s="4"/>
+      <c r="K135" s="6"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="35"/>
+      <c r="O135" s="35"/>
+      <c r="P135" s="35"/>
+      <c r="Q135" s="35"/>
+      <c r="R135" s="35"/>
+      <c r="S135" s="35"/>
+      <c r="T135" s="35"/>
+      <c r="U135" s="35"/>
+      <c r="V135" s="35"/>
+      <c r="W135" s="35"/>
+      <c r="X135" s="35"/>
+      <c r="Y135" s="35"/>
+      <c r="Z135" s="35"/>
+    </row>
+    <row r="136" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A136" s="2">
+        <v>132</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G136" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H136" s="4">
+        <v>1</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="J136" s="4"/>
+      <c r="K136" s="6"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="35"/>
+      <c r="O136" s="35"/>
+      <c r="P136" s="35"/>
+      <c r="Q136" s="35"/>
+      <c r="R136" s="35"/>
+      <c r="S136" s="35"/>
+      <c r="T136" s="35"/>
+      <c r="U136" s="35"/>
+      <c r="V136" s="35"/>
+      <c r="W136" s="35"/>
+      <c r="X136" s="35"/>
+      <c r="Y136" s="35"/>
+      <c r="Z136" s="35"/>
+    </row>
+    <row r="137" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A137" s="2">
+        <v>133</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G137" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H137" s="4">
+        <v>1</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="J137" s="4"/>
+      <c r="K137" s="6"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="35"/>
+      <c r="O137" s="35"/>
+      <c r="P137" s="35"/>
+      <c r="Q137" s="35"/>
+      <c r="R137" s="35"/>
+      <c r="S137" s="35"/>
+      <c r="T137" s="35"/>
+      <c r="U137" s="35"/>
+      <c r="V137" s="35"/>
+      <c r="W137" s="35"/>
+      <c r="X137" s="35"/>
+      <c r="Y137" s="35"/>
+      <c r="Z137" s="35"/>
+    </row>
+    <row r="138" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A138" s="2">
+        <v>134</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G138" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H138" s="4">
+        <v>1</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="J138" s="4"/>
+      <c r="K138" s="6"/>
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
+      <c r="N138" s="35"/>
+      <c r="O138" s="35"/>
+      <c r="P138" s="35"/>
+      <c r="Q138" s="35"/>
+      <c r="R138" s="35"/>
+      <c r="S138" s="35"/>
+      <c r="T138" s="35"/>
+      <c r="U138" s="35"/>
+      <c r="V138" s="35"/>
+      <c r="W138" s="35"/>
+      <c r="X138" s="35"/>
+      <c r="Y138" s="35"/>
+      <c r="Z138" s="35"/>
+    </row>
+    <row r="139" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A139" s="2">
+        <v>135</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G139" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H139" s="4">
+        <v>1</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="J139" s="4"/>
+      <c r="K139" s="6"/>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="35"/>
+      <c r="O139" s="35"/>
+      <c r="P139" s="35"/>
+      <c r="Q139" s="35"/>
+      <c r="R139" s="35"/>
+      <c r="S139" s="35"/>
+      <c r="T139" s="35"/>
+      <c r="U139" s="35"/>
+      <c r="V139" s="35"/>
+      <c r="W139" s="35"/>
+      <c r="X139" s="35"/>
+      <c r="Y139" s="35"/>
+      <c r="Z139" s="35"/>
+    </row>
+    <row r="140" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A140" s="2">
+        <v>136</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G140" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H140" s="4">
+        <v>1</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="J140" s="4"/>
+      <c r="K140" s="6"/>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="35"/>
+      <c r="O140" s="35"/>
+      <c r="P140" s="35"/>
+      <c r="Q140" s="35"/>
+      <c r="R140" s="35"/>
+      <c r="S140" s="35"/>
+      <c r="T140" s="35"/>
+      <c r="U140" s="35"/>
+      <c r="V140" s="35"/>
+      <c r="W140" s="35"/>
+      <c r="X140" s="35"/>
+      <c r="Y140" s="35"/>
+      <c r="Z140" s="35"/>
+    </row>
+    <row r="141" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A141" s="2">
+        <v>137</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G141" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H141" s="4">
+        <v>1</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="J141" s="4"/>
+      <c r="K141" s="6"/>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="35"/>
+      <c r="O141" s="35"/>
+      <c r="P141" s="35"/>
+      <c r="Q141" s="35"/>
+      <c r="R141" s="35"/>
+      <c r="S141" s="35"/>
+      <c r="T141" s="35"/>
+      <c r="U141" s="35"/>
+      <c r="V141" s="35"/>
+      <c r="W141" s="35"/>
+      <c r="X141" s="35"/>
+      <c r="Y141" s="35"/>
+      <c r="Z141" s="35"/>
+    </row>
+    <row r="142" spans="1:26" ht="28" x14ac:dyDescent="0.2">
+      <c r="A142" s="2">
+        <v>138</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G142" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H142" s="4">
+        <v>1</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J142" s="4"/>
+      <c r="K142" s="6"/>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="35"/>
+      <c r="O142" s="35"/>
+      <c r="P142" s="35"/>
+      <c r="Q142" s="35"/>
+      <c r="R142" s="35"/>
+      <c r="S142" s="35"/>
+      <c r="T142" s="35"/>
+      <c r="U142" s="35"/>
+      <c r="V142" s="35"/>
+      <c r="W142" s="35"/>
+      <c r="X142" s="35"/>
+      <c r="Y142" s="35"/>
+      <c r="Z142" s="35"/>
+    </row>
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6768,26 +8255,26 @@
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F116">
+  <conditionalFormatting sqref="F5:F142">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Easy">
       <formula>NOT(ISERROR(SEARCH("Easy",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F116">
+  <conditionalFormatting sqref="F5:F142">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F116">
+  <conditionalFormatting sqref="F5:F142">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Hard">
       <formula>NOT(ISERROR(SEARCH("Hard",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E116" xr:uid="{9EFEB563-C64F-1745-AFE0-E6E1C11659D8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E116 E117:E138 E139:E142" xr:uid="{9EFEB563-C64F-1745-AFE0-E6E1C11659D8}">
       <formula1>"All-Time,Single-Season,Recent,Awards,Matchups,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F116" xr:uid="{164C0A98-2A9C-404F-B8E2-3525B96E6A3C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F116 F117:F138 F139:F142" xr:uid="{164C0A98-2A9C-404F-B8E2-3525B96E6A3C}">
       <formula1>"Easy,Medium,Hard"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6882,10 +8369,36 @@
     <hyperlink ref="I114" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
     <hyperlink ref="I115" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
     <hyperlink ref="I116" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="G117" r:id="rId91" display="https://www.pro-football-reference.com/players/R/RodgAa00/touchdowns/passing" xr:uid="{D1EE9800-E2E2-9044-9A4A-499E4FDC4938}"/>
+    <hyperlink ref="G118" r:id="rId92" display="https://www.pro-football-reference.com/players/B/BradTo00/touchdowns/passing" xr:uid="{433E2DCA-13F1-9C4A-B31A-7FC181C88BB9}"/>
+    <hyperlink ref="G119" r:id="rId93" display="https://www.pro-football-reference.com/players/B/BreeDr00/touchdowns/passing" xr:uid="{445A00F0-890C-314E-81AC-D436972A2F87}"/>
+    <hyperlink ref="G120" r:id="rId94" display="https://www.pro-football-reference.com/players/M/MannPe00/touchdowns/passing" xr:uid="{990D7AFA-5104-534A-8E5B-797A0D6FC4E5}"/>
+    <hyperlink ref="G121" r:id="rId95" display="https://www.pro-football-reference.com/players/F/FavrBr00/touchdowns/passing" xr:uid="{8BBC8F64-FB5E-A344-9357-15BE975AC6B9}"/>
+    <hyperlink ref="G122" r:id="rId96" display="https://www.pro-football-reference.com/players/R/RivePh00/touchdowns/passing" xr:uid="{2737DF5D-1EAF-8B48-A9B5-02120CE2C938}"/>
+    <hyperlink ref="G123" r:id="rId97" display="https://www.pro-football-reference.com/players/S/StafMa00/touchdowns/passing" xr:uid="{1CC6A871-EF7A-3341-AAFF-9A76001FDC11}"/>
+    <hyperlink ref="G124" r:id="rId98" display="https://www.pro-football-reference.com/players/M/MariDa00/touchdowns/passing" xr:uid="{1D3D48E5-8186-1549-ACF6-F38A7F559032}"/>
+    <hyperlink ref="G125" r:id="rId99" display="https://www.pro-football-reference.com/players/R/RoetBe00/touchdowns/passing" xr:uid="{C13C9312-0338-B24D-951C-A73F4C6A7109}"/>
+    <hyperlink ref="G126" r:id="rId100" display="https://www.pro-football-reference.com/players/R/RyanMa00/touchdowns/passing" xr:uid="{1057DC9E-59B4-C544-8550-ABC1107A9575}"/>
+    <hyperlink ref="G127" r:id="rId101" display="https://www.pro-football-reference.com/players/M/MannEl00/touchdowns/passing" xr:uid="{96D1032F-3F55-E648-A40D-CA1E520B537B}"/>
+    <hyperlink ref="G128" r:id="rId102" display="https://www.pro-football-reference.com/players/W/WilsRu00/touchdowns/passing" xr:uid="{2D355718-53DC-CD44-8E7A-2B03982A82B5}"/>
+    <hyperlink ref="G129" r:id="rId103" display="https://www.pro-football-reference.com/players/T/TarkFr00/touchdowns/passing" xr:uid="{43B618D6-31C0-C341-9506-3840E186816C}"/>
+    <hyperlink ref="G130" r:id="rId104" display="https://www.pro-football-reference.com/players/E/ElwaJo00/touchdowns/passing" xr:uid="{224FBD48-4170-A749-93B8-3D5ACA8CE214}"/>
+    <hyperlink ref="G131" r:id="rId105" display="https://www.pro-football-reference.com/players/C/CousKi00/touchdowns/passing" xr:uid="{C87F684C-4440-9E40-B8D2-A6F14936727B}"/>
+    <hyperlink ref="G132" r:id="rId106" display="https://www.pro-football-reference.com/players/P/PalmCa00/touchdowns/passing" xr:uid="{0CC01E8A-D0D7-1841-8A4C-F2D9519BC58C}"/>
+    <hyperlink ref="G133" r:id="rId107" display="https://www.pro-football-reference.com/players/M/MoonWa00/touchdowns/passing" xr:uid="{13C8CEAD-6EE2-8841-B7A4-26E29A612264}"/>
+    <hyperlink ref="G134" r:id="rId108" display="https://www.pro-football-reference.com/players/U/UnitJo00/touchdowns/passing" xr:uid="{0DBAAE7D-E273-B14B-92D1-A32201FA81C0}"/>
+    <hyperlink ref="G135" r:id="rId109" display="https://www.pro-football-reference.com/players/T/TestVi00/touchdowns/passing" xr:uid="{9B6B9445-89BA-554B-9817-348A05123FE7}"/>
+    <hyperlink ref="G136" r:id="rId110" display="https://www.pro-football-reference.com/players/M/MontJo01/touchdowns/passing" xr:uid="{B40378EF-094E-8F41-BA58-C7083ECCE67C}"/>
+    <hyperlink ref="G137" r:id="rId111" display="https://www.pro-football-reference.com/players/F/FlacJo00/touchdowns/passing" xr:uid="{7C672007-E096-594D-A930-2F0A54AEABBB}"/>
+    <hyperlink ref="G138" r:id="rId112" display="https://www.pro-football-reference.com/players/M/MahoPa00/touchdowns/passing" xr:uid="{F9C6277C-CBC0-0942-8A6A-6E17BAE5BEEE}"/>
+    <hyperlink ref="G139" r:id="rId113" display="https://www.pro-football-reference.com/players/K/KrieDa00/touchdowns/passing" xr:uid="{5E3F252B-4D62-9449-9F0D-F4F09A6B1927}"/>
+    <hyperlink ref="G140" r:id="rId114" display="https://www.pro-football-reference.com/players/C/CarrDe02/touchdowns/passing" xr:uid="{CD5DC9AA-4E76-EC40-8B44-E06A9DACE4C7}"/>
+    <hyperlink ref="G141" r:id="rId115" display="https://www.pro-football-reference.com/players/G/GoffJa00/touchdowns/passing" xr:uid="{F4006F48-9D6B-CE4F-B9BB-F5F61B8D36D9}"/>
+    <hyperlink ref="G142" r:id="rId116" display="https://www.pro-football-reference.com/players/J/JurgSo00/touchdowns/passing" xr:uid="{1EB026E9-973A-A44B-8F14-E3134F15C604}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId91"/>
+  <legacyDrawing r:id="rId117"/>
 </worksheet>
 </file>
 
